--- a/kadai_kanri_simple.xlsx
+++ b/kadai_kanri_simple.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\toush\Desktop\works\hayashi_work\program\AIEvaluateToDoList\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A619045-2040-4CEA-B3CD-68EA9E819909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447DB521-5699-4E22-8BAD-F0EB97CD75DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="0" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="課題管理表" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>No.</t>
   </si>
@@ -76,51 +89,6 @@
 ZZZ</t>
   </si>
   <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-0.5人日
-2025-10-29 20:45:20 model:gpt-5
-1人日</t>
-  </si>
-  <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-中
-2025-10-29 20:45:20 model:gpt-5
-中</t>
-  </si>
-  <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-進め方の注意点を簡潔に（DRY-RUN）
-2025-10-29 20:45:20 model:gpt-5
-・情報テンプレートを使いヒアリング（現象／期待値／前提／変更点）を標準化
-・期間限定でログレベル引き上げや分散トレースを有効化
-・本番データはマスキングとアクセス権管理を厳守
-・原因仮説ごとに検証計画を作成し優先度順に実行
-・影響大の場合のエスカレーション基準と暫定回避策を先に合意
-・結果は再現手順・原因・対処・再発防止までドキュメント化</t>
-  </si>
-  <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-現状から見た妥当な評価（DRY-RUN）
-2025-10-29 20:45:20 model:gpt-5
-・No.1：〇〇の不具合調査／ステータス：未着手
-・人員：1名（担当：佐藤）
-・現状把握：2025/10/28、2025/10/29ともに「ZZZ」で詳細不明
-・備考：調査開始は明日予定（2025/10/30）
-・総合評価：情報不足により影響範囲・再現性が未確定。早急な情報収集と切り分け、初期タイムボックス設定が必要</t>
-  </si>
-  <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-・依存関係の確認
-・レビュー観点の事前共有
-2025-10-29 20:45:20 model:gpt-5
-・現状把握が「ZZZ」で不明瞭なため情報欠落による調査遅延リスク
-・ログ保全前の再起動・ローテーションで証跡が消失する恐れ
-・本番環境での直接操作は変更管理と承認フローを厳守
-・再現不可時の打ち切り基準と次の仮説への切替条件を明確化
-・担当者1名のためボトルネック化リスク。バックアップ担当を用意
-・関係者への定期ステータス報告と合意形成をルーチン化</t>
-  </si>
-  <si>
     <t>調査開始は明日予定</t>
   </si>
   <si>
@@ -133,62 +101,6 @@
     <t>鈴木</t>
   </si>
   <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-0.5人日
-2025-10-29 20:45:20 model:gpt-5
-2人日</t>
-  </si>
-  <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-中
-2025-10-29 20:45:20 model:gpt-5
-低</t>
-  </si>
-  <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-次の具体的な一手を簡潔に記載（DRY-RUN）
-2025-10-29 20:45:20 model:gpt-5
-・対象範囲とカバレッジ(要件/仕様とのトレーサビリティ)を明確化
-・現状「ZZZ」の記載を具体的な進捗/残件/ブロッカーに更新
-・テストケースのテンプレート/命名規約を確定し、初版を一括登録
-・クリティカル機能から優先度高のケースを先行作成
-・田中さんと最終レビュー日程・観点チェックリストを確定
-・レビュー前にセルフチェック(同値・境界・異常・回帰の網羅)を実施</t>
-  </si>
-  <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-進め方の注意点を簡潔に（DRY-RUN）
-2025-10-29 20:45:20 model:gpt-5
-・要件⇔テストのトレーサビリティマトリクスを作成して抜け漏れ防止
-・テスト設計技法(同値分類/境界値/状態遷移/決定表)を活用
-・テストデータ生成とケースID採番を標準化し再利用性を高める
-・進捗は日次で可視化し、抽象語「ZZZ」は廃止して定量指標(作成件数/完了率)で報告
-・レビュー指摘はカテゴリ分けして再発防止チェックリストに反映</t>
-  </si>
-  <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-現状から見た妥当な評価（DRY-RUN）
-2025-10-29 20:45:20 model:gpt-5
-・No.2「テストケース作成」は対応中、更新は10/28・10/29ありも内容が不明瞭(ZZZ)
-・人員:1名(鈴木)で実施、最終レビュー:田中予定で役割は概ね明確
-・カバレッジ/優先度/レビュー日程が未確定で不確実性あり
-・仕様確定度合いに依存、レビュー待ちの滞留リスクは小〜中
-・総合評価: 難易度は並。進捗可視化とレビュー確約でリスク低減可能</t>
-  </si>
-  <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-・依存関係の確認
-・レビュー観点の事前共有
-2025-10-29 20:45:20 model:gpt-5
-・進捗記録が抽象的(ZZZ)なままだと状況判断不可
-・カバレッジ不足や重要シナリオの抜け漏れ
-・レビュー日程未確定による最終品質保証の遅延
-・単独作業による観点の偏り
-・仕様変更の影響をケースに反映し忘れる
-・命名/フォーマット不統一でレビュー効率低下
-・テスト管理ツール未使用による版管理ミス</t>
-  </si>
-  <si>
     <t>最終レビューは田中さん担当</t>
   </si>
   <si>
@@ -205,67 +117,6 @@
   </si>
   <si>
     <t>仕様書の更新</t>
-  </si>
-  <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-次の具体的な一手を簡潔に記載（DRY-RUN）
-2025-10-29 20:45:20 model:gpt-5
-・関係者（要件/設計/開発/QA）へ更新範囲・対象バージョン・締切をヒアリング
-・既存仕様書の最新版を取得し、変更点の差分箇所を洗い出し
-・根拠資料（要件変更、設計変更、チケット、議事録）を収集・整理
-・目次とテンプレートを確定し、章立て/用語を統一
-・ドラフト版を作成し、レビューアを指名してレビュー日程を確定
-・レビュー指摘を反映し、版番号・変更履歴を更新
-・配布/リポジトリ反映、関係者周知、課題管理表のステータス更新</t>
-  </si>
-  <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-進め方の注意点を簡潔に（DRY-RUN）
-2025-10-29 20:45:20 model:gpt-5
-・更新スコープを先に固定して追加要望は別チケット化
-・版管理（版番号/変更履歴/日付/作成者）を厳密に運用
-・用語集とスタイルガイドを設定して記述揺れを防止
-・差分中心で記載し、根拠リンクを明記して追跡可能性を担保
-・レビュー観点チェックリスト（完全性/一貫性/テスト可能性）を活用
-・締切から逆算したミニマムドラフト→1回集中レビューで短期決着
-・自動生成可能部分（API定義、ER、シーケンス）はツール活用
-・承認者を明確化し、承認前配布を禁止</t>
-  </si>
-  <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-現状から見た妥当な評価（DRY-RUN）
-2025-10-29 20:45:20 model:gpt-5
-・No.4 仕様書の更新：ステータス＝未着手。担当：HK、人員：1。現状把握：2025-10-29 00:00:00
-・スコープ未確定の可能性が高く、開始時ヒアリング必須。想定工数：約1人日（レビュー含め増減あり）
-・総合評価：早期着手で短期完了見込み。レビュー確保と版管理が成否の鍵</t>
-  </si>
-  <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-・依存関係の確認
-・レビュー観点の事前共有
-2025-10-29 20:45:20 model:gpt-5
-・スコープ膨張による工数超過
-・参照元（要件・設計・コード）の最新版未反映
-・用語・書式の不統一でレビュー指摘増大
-・レビューア確保遅延によるスケジュール滑り
-・版番号・変更履歴・配布先の更新漏れ
-・機密情報の取り扱いミス（外部配布版のマスキング）
-・関連チケット・変更要求との整合性欠如
-・テスト観点との不整合により後工程で手戻り</t>
-  </si>
-  <si>
-    <t>2025-10-29 20:42:33 model:gpt-5
-次の具体的な一手を簡潔に記載（DRY-RUN）
-2025-10-29 20:45:20 model:gpt-5
-・10/30の調査キックオフを設定し着手確認
-・依頼元から事象概要／再現手順／発生頻度／影響範囲を聴取
-・対象環境・バージョン・直近変更履歴の収集
-・発生時刻の各種ログ／メトリクス／アラートの保全と取得計画
-・再現環境を準備し再現と切り分け（アプリ／DB／ネットワーク／外部API）
-・既知事象・直近リリース差分・エラーメッセージの照合
-・初期調査タイムボックス（1人日）と中間報告タイミングの合意
-・チケット細分化（ログ収集、再現、仮説検証）と担当・期限設定</t>
-    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -330,7 +181,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -346,9 +197,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -360,9 +208,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -371,7 +216,15 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -708,50 +561,50 @@
     <col min="2" max="2" width="25.25" style="1" customWidth="1"/>
     <col min="3" max="4" width="10.83203125" style="2" customWidth="1"/>
     <col min="5" max="5" width="9" style="2" customWidth="1"/>
-    <col min="6" max="6" width="36.4140625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="36.4140625" style="5" customWidth="1"/>
     <col min="7" max="8" width="8.6640625" style="2" customWidth="1"/>
-    <col min="9" max="12" width="36.4140625" style="6" customWidth="1"/>
+    <col min="9" max="12" width="36.4140625" style="5" customWidth="1"/>
     <col min="13" max="13" width="16.58203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -771,29 +624,17 @@
       <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -801,40 +642,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>31</v>
-      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
       <c r="M3" s="4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -842,28 +671,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
       <c r="M4" s="4" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -871,7 +700,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>14</v>
@@ -880,29 +709,17 @@
         <v>1</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="10">
+        <v>24</v>
+      </c>
+      <c r="F5" s="9">
         <v>45959</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
       <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -911,13 +728,13 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="7"/>
+      <c r="F6" s="9"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -926,13 +743,13 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="7"/>
+      <c r="F7" s="9"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
       <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -941,13 +758,13 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="7"/>
+      <c r="F8" s="9"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
       <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -956,13 +773,13 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="7"/>
+      <c r="F9" s="9"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -971,13 +788,13 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="7"/>
+      <c r="F10" s="9"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -986,13 +803,13 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="7"/>
+      <c r="F11" s="9"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1001,13 +818,13 @@
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="7"/>
+      <c r="F12" s="9"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
       <c r="M12" s="4"/>
     </row>
     <row r="13" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1016,13 +833,13 @@
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="7"/>
+      <c r="F13" s="9"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
       <c r="M13" s="4"/>
     </row>
     <row r="14" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1031,13 +848,13 @@
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="7"/>
+      <c r="F14" s="9"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1046,13 +863,13 @@
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="7"/>
+      <c r="F15" s="9"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
       <c r="M15" s="4"/>
     </row>
     <row r="16" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1061,13 +878,13 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="7"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
       <c r="M16" s="4"/>
     </row>
     <row r="17" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1076,13 +893,13 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="7"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
       <c r="M17" s="4"/>
     </row>
     <row r="18" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1091,13 +908,13 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="7"/>
+      <c r="F18" s="9"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
       <c r="M18" s="4"/>
     </row>
     <row r="19" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1106,17 +923,22 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="7"/>
+      <c r="F19" s="9"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
       <c r="M19" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="A2:M19">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$C2="完了"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.11811023622047249" bottom="0.23622047244094491" header="0.31496062992125978" footer="0.31496062992125978"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
